--- a/app/www/profiles/profile-Wine-noesy-400.xlsx
+++ b/app/www/profiles/profile-Wine-noesy-400.xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workdir\Metabolomic\NMRProcFlow\git\RnmrQuant1D\RnmrQuant1D_UI\www\profiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workdir\Metabolomic\WAP-NMR\Manips\JC-DUB-400\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B7BA78-9AF9-4BF2-B08F-4A205A343CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3BA353-6AF7-44F5-9CFE-5DE702639694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4488" yWindow="864" windowWidth="17280" windowHeight="9960" xr2:uid="{8B82BC10-3820-44B4-9766-BAF901DAB81B}"/>
+    <workbookView xWindow="1170" yWindow="345" windowWidth="25575" windowHeight="14265" xr2:uid="{8B82BC10-3820-44B4-9766-BAF901DAB81B}"/>
   </bookViews>
   <sheets>
     <sheet name="NOESY" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="112">
   <si>
     <t>#=====================================================================</t>
   </si>
@@ -241,9 +241,6 @@
     <t>r5</t>
   </si>
   <si>
-    <t>4.316,4.349,0,1.4,0.3</t>
-  </si>
-  <si>
     <t>beta_glucose</t>
   </si>
   <si>
@@ -256,9 +253,6 @@
     <t>alpha_glucose</t>
   </si>
   <si>
-    <t>5.206,5.218,0,1.4,0.12</t>
-  </si>
-  <si>
     <t>galacturonic acid</t>
   </si>
   <si>
@@ -271,24 +265,12 @@
     <t>catechine</t>
   </si>
   <si>
-    <t>5.987,5.994,3,2,1,70</t>
-  </si>
-  <si>
     <t>5.974,6.012,5.99,d</t>
   </si>
   <si>
-    <t>6.075,6.084,3,2,1,70</t>
-  </si>
-  <si>
     <t>epicatechine</t>
   </si>
   <si>
-    <t>6.056,6.063,3,2,1,70</t>
-  </si>
-  <si>
-    <t>6.088,6.094,3,2,1,70</t>
-  </si>
-  <si>
     <t>caffeic acid</t>
   </si>
   <si>
@@ -352,16 +334,28 @@
     <t>7.123,7.1535,7.14,s</t>
   </si>
   <si>
-    <t>2.907,2.917,1,1.4,0.3</t>
-  </si>
-  <si>
-    <t>2.866,2.876,1,1.6,0.4</t>
-  </si>
-  <si>
     <t>2.896,2.925,2.912,d</t>
   </si>
   <si>
-    <t>0,2,0.5</t>
+    <t>0,2,0.5,150</t>
+  </si>
+  <si>
+    <t>5.206,5.218,0,5,0.6,150</t>
+  </si>
+  <si>
+    <t>4.316,4.349,0,2,0.3,70</t>
+  </si>
+  <si>
+    <t>2.866,2.876,1,1.7,0.6,70</t>
+  </si>
+  <si>
+    <t>2.907,2.917,1,1.7,0.6,70</t>
+  </si>
+  <si>
+    <t>0,1.4,0.3,70</t>
+  </si>
+  <si>
+    <t>6.05,6.105,6.078,d</t>
   </si>
 </sst>
 </file>
@@ -889,7 +883,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -918,6 +912,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1325,179 +1325,179 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA5D7C91-0D6C-4DDA-8295-E72EAE8DA3E7}">
   <dimension ref="A1:K107"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="5" max="5" width="21.109375" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" customWidth="1"/>
-    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
     </row>
-    <row r="35" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>28</v>
       </c>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="G35" s="4"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>34</v>
       </c>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="G36" s="5"/>
     </row>
-    <row r="39" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>28</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>41</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>42</v>
@@ -1571,7 +1571,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>46</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>46</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>46</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>46</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>46</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>46</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>46</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>46</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>46</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>46</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>46</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>46</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
         <v>46</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
         <v>46</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>46</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
         <v>46</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
         <v>28</v>
       </c>
@@ -2105,20 +2105,20 @@
       <c r="G58" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H58" s="10" t="s">
+      <c r="H58" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="I58" s="10" t="s">
+      <c r="I58" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="J58" s="10" t="s">
+      <c r="J58" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="K58" s="10" t="s">
+      <c r="K58" s="16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
         <v>56</v>
       </c>
@@ -2140,20 +2140,20 @@
       <c r="G59" s="13">
         <v>0</v>
       </c>
-      <c r="H59" s="12">
+      <c r="H59" s="17">
         <v>6</v>
       </c>
-      <c r="I59" s="12">
-        <v>1</v>
-      </c>
-      <c r="J59" s="12">
-        <v>1</v>
-      </c>
-      <c r="K59" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I59" s="17">
+        <v>1</v>
+      </c>
+      <c r="J59" s="17">
+        <v>1</v>
+      </c>
+      <c r="K59" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
         <v>56</v>
       </c>
@@ -2175,20 +2175,20 @@
       <c r="G60" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="H60" s="12">
+      <c r="H60" s="17">
         <v>6</v>
       </c>
-      <c r="I60" s="12">
+      <c r="I60" s="17">
         <v>3</v>
       </c>
-      <c r="J60" s="12">
-        <v>1</v>
-      </c>
-      <c r="K60" s="12">
+      <c r="J60" s="17">
+        <v>1</v>
+      </c>
+      <c r="K60" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
         <v>56</v>
       </c>
@@ -2210,20 +2210,20 @@
       <c r="G61" s="13">
         <v>0</v>
       </c>
-      <c r="H61" s="12">
+      <c r="H61" s="17">
         <v>6</v>
       </c>
-      <c r="I61" s="12">
+      <c r="I61" s="17">
         <v>3</v>
       </c>
-      <c r="J61" s="12">
-        <v>1</v>
-      </c>
-      <c r="K61" s="12">
+      <c r="J61" s="17">
+        <v>1</v>
+      </c>
+      <c r="K61" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
         <v>56</v>
       </c>
@@ -2245,20 +2245,20 @@
       <c r="G62" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="H62" s="12">
+      <c r="H62" s="17">
         <v>6</v>
       </c>
-      <c r="I62" s="12">
+      <c r="I62" s="17">
         <v>4</v>
       </c>
-      <c r="J62" s="12">
-        <v>1</v>
-      </c>
-      <c r="K62" s="12">
+      <c r="J62" s="17">
+        <v>1</v>
+      </c>
+      <c r="K62" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
         <v>56</v>
       </c>
@@ -2275,25 +2275,25 @@
         <v>4.5</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="H63" s="12">
+        <v>104</v>
+      </c>
+      <c r="H63" s="17">
         <v>25</v>
       </c>
-      <c r="I63" s="12">
+      <c r="I63" s="17">
         <v>0.5</v>
       </c>
-      <c r="J63" s="12">
-        <v>1</v>
-      </c>
-      <c r="K63" s="12">
+      <c r="J63" s="17">
+        <v>1</v>
+      </c>
+      <c r="K63" s="17">
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
         <v>56</v>
       </c>
@@ -2310,25 +2310,25 @@
         <v>4.5</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="H64" s="12">
+        <v>104</v>
+      </c>
+      <c r="H64" s="17">
         <v>25</v>
       </c>
-      <c r="I64" s="12">
+      <c r="I64" s="17">
         <v>0.5</v>
       </c>
-      <c r="J64" s="12">
-        <v>1</v>
-      </c>
-      <c r="K64" s="12">
+      <c r="J64" s="17">
+        <v>1</v>
+      </c>
+      <c r="K64" s="17">
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
         <v>56</v>
       </c>
@@ -2350,20 +2350,20 @@
       <c r="G65" s="13">
         <v>0</v>
       </c>
-      <c r="H65" s="12">
+      <c r="H65" s="17">
         <v>20</v>
       </c>
-      <c r="I65" s="12">
+      <c r="I65" s="17">
         <v>2</v>
       </c>
-      <c r="J65" s="12">
-        <v>1</v>
-      </c>
-      <c r="K65" s="12">
+      <c r="J65" s="17">
+        <v>1</v>
+      </c>
+      <c r="K65" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
         <v>56</v>
       </c>
@@ -2380,30 +2380,30 @@
         <v>7</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="G66" s="13">
         <v>0</v>
       </c>
-      <c r="H66" s="12">
+      <c r="H66" s="17">
         <v>25</v>
       </c>
-      <c r="I66" s="12">
+      <c r="I66" s="17">
         <v>2</v>
       </c>
-      <c r="J66" s="12">
+      <c r="J66" s="17">
         <v>1.333</v>
       </c>
-      <c r="K66" s="12">
+      <c r="K66" s="17">
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C67" s="13" t="s">
         <v>66</v>
@@ -2415,30 +2415,30 @@
         <v>7.9</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G67" s="13">
         <v>0</v>
       </c>
-      <c r="H67" s="12">
+      <c r="H67" s="17">
         <v>50</v>
       </c>
-      <c r="I67" s="12">
-        <v>1</v>
-      </c>
-      <c r="J67" s="12">
-        <v>1</v>
-      </c>
-      <c r="K67" s="12">
+      <c r="I67" s="17">
+        <v>1</v>
+      </c>
+      <c r="J67" s="17">
+        <v>1</v>
+      </c>
+      <c r="K67" s="17">
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C68" s="13" t="s">
         <v>60</v>
@@ -2453,27 +2453,27 @@
         <v>0</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="H68" s="12">
+        <v>75</v>
+      </c>
+      <c r="H68" s="17">
         <v>6</v>
       </c>
-      <c r="I68" s="12">
+      <c r="I68" s="17">
         <v>2</v>
       </c>
-      <c r="J68" s="12">
-        <v>1</v>
-      </c>
-      <c r="K68" s="12">
+      <c r="J68" s="17">
+        <v>1</v>
+      </c>
+      <c r="K68" s="17">
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C69" s="13" t="s">
         <v>72</v>
@@ -2485,30 +2485,30 @@
         <v>3.75</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="G69" s="13">
         <v>0</v>
       </c>
-      <c r="H69" s="12">
-        <v>20</v>
-      </c>
-      <c r="I69" s="12">
-        <v>1</v>
-      </c>
-      <c r="J69" s="12">
-        <v>1</v>
-      </c>
-      <c r="K69" s="12">
+      <c r="H69" s="17">
+        <v>18</v>
+      </c>
+      <c r="I69" s="17">
+        <v>1</v>
+      </c>
+      <c r="J69" s="17">
+        <v>1</v>
+      </c>
+      <c r="K69" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C70" s="13" t="s">
         <v>66</v>
@@ -2525,25 +2525,25 @@
       <c r="G70" s="13">
         <v>0</v>
       </c>
-      <c r="H70" s="12">
+      <c r="H70" s="17">
         <v>6</v>
       </c>
-      <c r="I70" s="12">
-        <v>1</v>
-      </c>
-      <c r="J70" s="12">
-        <v>1</v>
-      </c>
-      <c r="K70" s="12">
+      <c r="I70" s="17">
+        <v>1</v>
+      </c>
+      <c r="J70" s="17">
+        <v>1</v>
+      </c>
+      <c r="K70" s="17">
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C71" s="13" t="s">
         <v>60</v>
@@ -2555,30 +2555,30 @@
         <v>5.8120000000000003</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G71" s="13">
         <v>0</v>
       </c>
-      <c r="H71" s="12">
+      <c r="H71" s="17">
         <v>6</v>
       </c>
-      <c r="I71" s="12">
+      <c r="I71" s="17">
         <v>0.5</v>
       </c>
-      <c r="J71" s="12">
-        <v>1</v>
-      </c>
-      <c r="K71" s="12">
+      <c r="J71" s="17">
+        <v>1</v>
+      </c>
+      <c r="K71" s="17">
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C72" s="13" t="s">
         <v>60</v>
@@ -2590,170 +2590,170 @@
         <v>5.85</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G72" s="13">
         <v>0</v>
       </c>
-      <c r="H72" s="12">
+      <c r="H72" s="17">
         <v>6</v>
       </c>
-      <c r="I72" s="12">
+      <c r="I72" s="17">
         <v>0.5</v>
       </c>
-      <c r="J72" s="12">
-        <v>1</v>
-      </c>
-      <c r="K72" s="12">
+      <c r="J72" s="17">
+        <v>1</v>
+      </c>
+      <c r="K72" s="17">
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D73" s="13">
-        <v>5.99</v>
+        <v>5.984</v>
       </c>
       <c r="E73" s="13">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="F73" s="13" t="s">
-        <v>83</v>
+        <v>5.9969999999999999</v>
+      </c>
+      <c r="F73" s="13">
+        <v>2</v>
       </c>
       <c r="G73" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="H73" s="12">
+        <v>81</v>
+      </c>
+      <c r="H73" s="17">
         <v>5</v>
       </c>
-      <c r="I73" s="12">
-        <v>1</v>
-      </c>
-      <c r="J73" s="12">
-        <v>1</v>
-      </c>
-      <c r="K73" s="12">
+      <c r="I73" s="17">
+        <v>1</v>
+      </c>
+      <c r="J73" s="17">
+        <v>1</v>
+      </c>
+      <c r="K73" s="17">
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D74" s="13">
-        <v>6.0780000000000003</v>
+        <v>6.07</v>
       </c>
       <c r="E74" s="13">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="F74" s="13" t="s">
-        <v>85</v>
+        <v>6.0830000000000002</v>
+      </c>
+      <c r="F74" s="13">
+        <v>2</v>
       </c>
       <c r="G74" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="H74" s="12">
+        <v>111</v>
+      </c>
+      <c r="H74" s="17">
         <v>5</v>
       </c>
-      <c r="I74" s="12">
-        <v>1</v>
-      </c>
-      <c r="J74" s="12">
-        <v>1</v>
-      </c>
-      <c r="K74" s="12">
+      <c r="I74" s="17">
+        <v>1</v>
+      </c>
+      <c r="J74" s="17">
+        <v>1</v>
+      </c>
+      <c r="K74" s="17">
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D75" s="13">
-        <v>6.06</v>
+        <v>6.0519999999999996</v>
       </c>
       <c r="E75" s="13">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="F75" s="13" t="s">
-        <v>87</v>
+        <v>6.0659999999999998</v>
+      </c>
+      <c r="F75" s="13">
+        <v>2</v>
       </c>
       <c r="G75" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="H75" s="12">
+        <v>111</v>
+      </c>
+      <c r="H75" s="17">
         <v>5</v>
       </c>
-      <c r="I75" s="12">
-        <v>1</v>
-      </c>
-      <c r="J75" s="12">
-        <v>1</v>
-      </c>
-      <c r="K75" s="12">
+      <c r="I75" s="17">
+        <v>1</v>
+      </c>
+      <c r="J75" s="17">
+        <v>1</v>
+      </c>
+      <c r="K75" s="17">
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D76" s="13">
-        <v>6.09</v>
+        <v>6.085</v>
       </c>
       <c r="E76" s="13">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="F76" s="13" t="s">
-        <v>88</v>
+        <v>6.0949999999999998</v>
+      </c>
+      <c r="F76" s="13">
+        <v>2</v>
       </c>
       <c r="G76" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="H76" s="12">
+        <v>111</v>
+      </c>
+      <c r="H76" s="17">
         <v>5</v>
       </c>
-      <c r="I76" s="12">
-        <v>1</v>
-      </c>
-      <c r="J76" s="12">
-        <v>1</v>
-      </c>
-      <c r="K76" s="12">
+      <c r="I76" s="17">
+        <v>1</v>
+      </c>
+      <c r="J76" s="17">
+        <v>1</v>
+      </c>
+      <c r="K76" s="17">
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C77" s="13" t="s">
         <v>66</v>
@@ -2764,31 +2764,31 @@
       <c r="E77" s="13">
         <v>16</v>
       </c>
-      <c r="F77" s="13">
-        <v>0</v>
+      <c r="F77" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="G77" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="H77" s="12">
+        <v>84</v>
+      </c>
+      <c r="H77" s="17">
         <v>5</v>
       </c>
-      <c r="I77" s="12">
-        <v>1</v>
-      </c>
-      <c r="J77" s="12">
-        <v>1</v>
-      </c>
-      <c r="K77" s="12">
+      <c r="I77" s="17">
+        <v>1</v>
+      </c>
+      <c r="J77" s="17">
+        <v>1</v>
+      </c>
+      <c r="K77" s="17">
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C78" s="13" t="s">
         <v>60</v>
@@ -2800,33 +2800,33 @@
         <v>6.7770000000000001</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G78" s="13">
         <v>0</v>
       </c>
-      <c r="H78" s="12">
+      <c r="H78" s="17">
         <v>6</v>
       </c>
-      <c r="I78" s="12">
+      <c r="I78" s="17">
         <v>2</v>
       </c>
-      <c r="J78" s="12">
-        <v>1</v>
-      </c>
-      <c r="K78" s="12">
+      <c r="J78" s="17">
+        <v>1</v>
+      </c>
+      <c r="K78" s="17">
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D79" s="13">
         <v>6.7869999999999999</v>
@@ -2835,33 +2835,33 @@
         <v>6.827</v>
       </c>
       <c r="F79" s="13" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G79" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="H79" s="12">
-        <v>4</v>
-      </c>
-      <c r="I79" s="12">
-        <v>1</v>
-      </c>
-      <c r="J79" s="12">
-        <v>1</v>
-      </c>
-      <c r="K79" s="12">
+        <v>89</v>
+      </c>
+      <c r="H79" s="17">
+        <v>9</v>
+      </c>
+      <c r="I79" s="17">
+        <v>1</v>
+      </c>
+      <c r="J79" s="17">
+        <v>1</v>
+      </c>
+      <c r="K79" s="17">
         <v>13</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D80" s="13">
         <v>6.8419999999999996</v>
@@ -2870,30 +2870,30 @@
         <v>8.6</v>
       </c>
       <c r="F80" s="13" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G80" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="H80" s="12">
+        <v>89</v>
+      </c>
+      <c r="H80" s="17">
         <v>6</v>
       </c>
-      <c r="I80" s="12">
-        <v>1</v>
-      </c>
-      <c r="J80" s="12">
-        <v>1</v>
-      </c>
-      <c r="K80" s="12">
+      <c r="I80" s="17">
+        <v>1</v>
+      </c>
+      <c r="J80" s="17">
+        <v>1</v>
+      </c>
+      <c r="K80" s="17">
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C81" s="13" t="s">
         <v>60</v>
@@ -2908,27 +2908,27 @@
         <v>1</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="H81" s="12">
+        <v>103</v>
+      </c>
+      <c r="H81" s="17">
         <v>6</v>
       </c>
-      <c r="I81" s="12">
+      <c r="I81" s="17">
         <v>2</v>
       </c>
-      <c r="J81" s="12">
-        <v>1</v>
-      </c>
-      <c r="K81" s="12">
+      <c r="J81" s="17">
+        <v>1</v>
+      </c>
+      <c r="K81" s="17">
         <v>14</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C82" s="13" t="s">
         <v>60</v>
@@ -2945,25 +2945,25 @@
       <c r="G82" s="13">
         <v>0</v>
       </c>
-      <c r="H82" s="12">
+      <c r="H82" s="17">
         <v>6</v>
       </c>
-      <c r="I82" s="12">
-        <v>1</v>
-      </c>
-      <c r="J82" s="12">
-        <v>1</v>
-      </c>
-      <c r="K82" s="12">
+      <c r="I82" s="17">
+        <v>1</v>
+      </c>
+      <c r="J82" s="17">
+        <v>1</v>
+      </c>
+      <c r="K82" s="17">
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C83" s="13" t="s">
         <v>60</v>
@@ -2975,40 +2975,40 @@
         <v>9.17</v>
       </c>
       <c r="F83" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G83" s="13">
         <v>0</v>
       </c>
-      <c r="H83" s="12">
+      <c r="H83" s="17">
         <v>6</v>
       </c>
-      <c r="I83" s="12">
-        <v>1</v>
-      </c>
-      <c r="J83" s="12">
-        <v>1</v>
-      </c>
-      <c r="K83" s="12">
+      <c r="I83" s="17">
+        <v>1</v>
+      </c>
+      <c r="J83" s="17">
+        <v>1</v>
+      </c>
+      <c r="K83" s="17">
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>47</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>88.147999999999996</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>47</v>
       </c>
@@ -3030,62 +3030,62 @@
         <v>60.052</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>47</v>
       </c>
       <c r="B89" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C89">
         <v>180.1559</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C90">
         <v>180.1559</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C91">
         <v>180.1574</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C92">
         <v>290.2681</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C93">
         <v>290.2681</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>47</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>88.11</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>47</v>
       </c>
@@ -3107,18 +3107,18 @@
         <v>118.13</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>47</v>
       </c>
       <c r="B96" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C96">
         <v>46.03</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>47</v>
       </c>
@@ -3129,40 +3129,40 @@
         <v>180.15600000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>47</v>
       </c>
       <c r="B98" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C98">
         <v>116.0722</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>47</v>
       </c>
       <c r="B99" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C99">
         <v>194.13939999999999</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>47</v>
       </c>
       <c r="B100" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C100">
         <v>170.11949999999999</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>47</v>
       </c>
@@ -3173,29 +3173,29 @@
         <v>134.0874</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>47</v>
       </c>
       <c r="B102" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C102">
         <v>174.15</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>47</v>
       </c>
       <c r="B103" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C103">
         <v>112.13</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>47</v>
       </c>
@@ -3206,34 +3206,34 @@
         <v>118.09</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>47</v>
       </c>
       <c r="B105" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C105">
         <v>137.136</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>47</v>
       </c>
       <c r="B106" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C106">
         <v>138.166</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>47</v>
       </c>
       <c r="B107" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C107">
         <v>148.07</v>
